--- a/3_Analysis/3_1_Content_Analysis/DATA/Correlation.xlsx
+++ b/3_Analysis/3_1_Content_Analysis/DATA/Correlation.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\桌面\缩减版\DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangh\Desktop\缩减版\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{351BAAA0-5FC0-4E71-8630-899090DDE6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3FCB80-C2F0-483B-B173-1940A2E987A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -43,7 +54,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,13 +69,47 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -76,16 +121,64 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{FB20DA64-583D-4628-BD35-9A9CB42E08CE}"/>
+    <cellStyle name="好 2" xfId="2" xr:uid="{CFBA2586-07D6-442B-B601-4B49C856B127}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -363,6 +456,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D88DDB07-6392-4850-9D24-1CA2B18C6102}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="22.6640625" style="8" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -371,320 +467,328 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26</v>
       </c>
-      <c r="B2">
-        <v>19</v>
-      </c>
-      <c r="C2">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B2" s="2">
+        <v>20</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.193362925733915</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>12</v>
       </c>
-      <c r="B3">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="3">
+        <v>13</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.19027250882673141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>19</v>
       </c>
-      <c r="B4">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="3">
+        <v>20</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.25107156086055649</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>32</v>
       </c>
-      <c r="B5">
-        <v>24</v>
-      </c>
-      <c r="C5">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>27</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.20248176881762814</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>21</v>
       </c>
-      <c r="B6">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.2170140234662517</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>20</v>
       </c>
-      <c r="B7">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>21</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.23253928195826118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C8" s="8">
+        <v>0.13752811986188906</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>23</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
+        <v>21</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.24511272764608291</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>20</v>
       </c>
-      <c r="C9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <v>10</v>
-      </c>
-      <c r="C10">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>9</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0.16536706454047304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>7</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>7</v>
       </c>
-      <c r="C11">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C11" s="8">
+        <v>0.18457438210553143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>23</v>
       </c>
-      <c r="B12">
-        <v>16</v>
-      </c>
-      <c r="C12">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>17</v>
+      </c>
+      <c r="C12" s="8">
+        <v>0.19651582111195603</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>24</v>
       </c>
-      <c r="B13">
-        <v>17</v>
-      </c>
-      <c r="C13">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0.1641726532319327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26</v>
       </c>
-      <c r="B14">
-        <v>26</v>
-      </c>
-      <c r="C14">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>33</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0.25234131996224501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>18</v>
       </c>
-      <c r="B15">
-        <v>14</v>
-      </c>
-      <c r="C15">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.19811447496959569</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
-      <c r="B16">
-        <v>16</v>
-      </c>
-      <c r="C16">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>20</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.23403097228028977</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>35</v>
       </c>
-      <c r="B17">
-        <v>29</v>
-      </c>
-      <c r="C17">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>31</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.22029669357389034</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>7</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="4">
         <v>7</v>
       </c>
-      <c r="C18">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C18" s="8">
+        <v>0.18023159784377218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>10</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
-      <c r="C19">
-        <v>0.21</v>
+      <c r="B19" s="2">
+        <v>13</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0.20748327422960097</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>4</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="5">
         <v>4</v>
       </c>
-      <c r="C20">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C20" s="8">
+        <v>0.10296375938477682</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>29</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>20</v>
       </c>
-      <c r="C21">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C21" s="8">
+        <v>0.20516163636161838</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>4</v>
       </c>
-      <c r="B22">
-        <v>4</v>
-      </c>
-      <c r="C22">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="3">
+        <v>7</v>
+      </c>
+      <c r="C22" s="8">
+        <v>0.15371809739654971</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>32</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <v>24</v>
       </c>
-      <c r="C23">
-        <v>0.19</v>
+      <c r="C23" s="8">
+        <v>0.18493576384048846</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2</v>
       </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="6">
+        <v>1</v>
+      </c>
+      <c r="C24" s="8">
+        <v>8.6262470112372619E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>20</v>
-      </c>
-      <c r="B25">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3">
         <v>11</v>
       </c>
-      <c r="C25">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C25" s="8">
+        <v>0.16807246669561951</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>7</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="3">
         <v>4</v>
       </c>
-      <c r="C26">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C26" s="8">
+        <v>0.15557281851258825</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>13</v>
       </c>
-      <c r="B27">
-        <v>12</v>
-      </c>
-      <c r="C27">
-        <v>0.24</v>
+      <c r="B27" s="3">
+        <v>13</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0.24028854123480062</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>15</v>
       </c>
-      <c r="B28">
-        <v>11</v>
-      </c>
-      <c r="C28">
-        <v>0.22</v>
+      <c r="B28" s="7">
+        <v>12</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.22313170526148379</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>10</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>8</v>
       </c>
-      <c r="C29">
-        <v>0.12</v>
+      <c r="C29" s="8">
+        <v>0.1217301550519293</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B29">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>